--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2475,4 +2476,2074 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Biological Safety Research Scientist</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safety Research</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5066977008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Data Scientist, Safeguards</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York City, NY; San Francisco, CA; Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5209196008</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Safeguards Interventions</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5322723008</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Safeguards Review Tooling</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5013366008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ML/Research Engineer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4949336008</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Product Manager, Safeguards (Child Safety)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5164820008</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Product Manager, Safeguards Rare Harms</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5139628008</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Product Manager, Safeguards (Verticals)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5097490008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Red Team Engineer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel Required) | San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5320469008</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Research Engineer (Senior Staff+), Safeguards Labs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5191785008</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Access Controls &amp; Identity</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319626008</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Account Takeover &amp; Credential Abuse</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319624008</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Age-Appropriate Design</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311234008</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Ban Evasion &amp; Recidivism</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319592008</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Bio Harms</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319696008</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Chem &amp; Explosives Harms</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319700008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Child Safety</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311237008</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safeguards Enforcement Analyst, Cyber Harm </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311159008</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Fraud &amp; Scams</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Safeguards, Fraud</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319554008</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safeguards Enforcement Analyst, Integrity &amp; Authenticity </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311149008</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Radiological &amp; Nuclear Harms</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319702008</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Safety Evaluations</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Washington, DC; San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Safeguards, Safety Evaluations</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5137183008</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Violence &amp; Extremism</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5343907008</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Safeguards Policy Analyst, Fraud &amp; Scams</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Safeguards, Fraud</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5174857008</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Financial Fraud</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5325909008</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4951844008</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Evals </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5251671008</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Infrastructure </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5074908008</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Safeguards ML Infrastructure</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4778843008</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Safeguards Review Tooling</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5342935008</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Safeguards (Infrastructure &amp; Evals)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5108695008</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Threat Intel Manager, Model Exploitation &amp; Fraud</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5305476008</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Credit Risk Strategy and Analytics</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8044686</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credit Risk Strategy and Analytics </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8052468</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Credit Risk Strategy Manager</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7863824</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fraud Operations Associate SDC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7651078</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Fraud Operations Manager</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7608396</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fraud Operations Manager (Mandarin-speaking)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7994541</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fraud Operations Team Lead</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7685460</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fraud Operations Team Lead</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8063857</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fraud Patterns Analyst</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>US-Remote</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7913410</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fraud Strategist</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8039803</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fraud Strategy Manager </t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remote </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8039729</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Head of User Risk Strategy</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7730667</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineering Manager - Fraud Detection</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8069506</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Payments Fraud Investigator</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7554002</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Payments Fraud Investigator</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>US-Remote</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7913406</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect, Radar (Fraud/Risk)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NY or SF</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7365914</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>User Risk Strategist, Ecosystem Risk Strategy</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>US-Chicago; US-Atlanta; US-Remote</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7977981</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Finance Business Partner, Trust &amp; Safety (6319)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7977161?gh_jid=7977161</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (Europe)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Amsterdam, North Holland, Netherlands</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7962542?gh_jid=7962542</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (LATAM)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7928938?gh_jid=7928938</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (SEA/ SA)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Gurugram, Haryana, India; India</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/8012671?gh_jid=8012671</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (SEA/SA)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7981917?gh_jid=7981917</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Fraud</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/8008607?gh_jid=8008607</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Trust and Safety</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Remote, CA, US</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7793344</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning Engineer, Responsible AI– Applied Research Science</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Remote, CA, US</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Responsible AI</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7494938</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Block/Cash App</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Staff Applied Machine Learning Engineer - Fraud &amp; Abuse</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Bay Area, CA, United States of America</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>http://block.xyz/careers/jobs/4969342008?gh_jid=4969342008</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Software Developer, Ops Platform and Fraud Investigations</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Toronto, Canada</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7737164?t=gh_src=&amp;gh_jid=7737164</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Product Manager, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/chime/jobs/8530184002?gh_jid=8530184002</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Software Engineer, Fraud &amp; Identity</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>New York, NY (HQ)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/8fa367de-71ba-409e-befd-175a163acb1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fraud &amp; Identity Specialist (Contract)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=4995818</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Specialist, Law Enforcement Response</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8001105</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,2022 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Biological Safety Research Scientist</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safety Research</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5066977008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Data Scientist, Safeguards</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New York City, NY; San Francisco, CA; Seattle, WA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5209196008</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Engineering Manager, Safeguards Interventions</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5322723008</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Engineering Manager, Safeguards Review Tooling</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5013366008</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ML/Research Engineer, Safeguards</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/4949336008</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Product Manager, Safeguards (Child Safety)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5164820008</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Product Manager, Safeguards Rare Harms</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5139628008</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Product Manager, Safeguards (Verticals)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5097490008</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Red Team Engineer, Safeguards</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Remote-Friendly (Travel Required) | San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5320469008</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Research Engineer (Senior Staff+), Safeguards Labs</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5191785008</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Access Controls &amp; Identity</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319626008</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Account Takeover &amp; Credential Abuse</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319624008</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Age-Appropriate Design</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311234008</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Ban Evasion &amp; Recidivism</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319592008</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Bio Harms</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319696008</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Chem &amp; Explosives Harms</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319700008</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Child Safety</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311237008</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Safeguards Enforcement Analyst, Cyber Harm </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311159008</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Fraud &amp; Scams</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Safeguards, Fraud</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319554008</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Safeguards Enforcement Analyst, Integrity &amp; Authenticity </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311149008</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Radiological &amp; Nuclear Harms</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319702008</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Safety Evaluations</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Washington, DC; San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Safeguards, Safety Evaluations</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5137183008</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Violence &amp; Extremism</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5343907008</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Safeguards Policy Analyst, Fraud &amp; Scams</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Safeguards, Fraud</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5174857008</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Staff+ Software Engineer, Financial Fraud</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5325909008</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Staff+ Software Engineer, Safeguards</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/4951844008</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Evals </t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5251671008</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Infrastructure </t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5074908008</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Staff+ Software Engineer, Safeguards ML Infrastructure</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/4778843008</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Staff+ Software Engineer, Safeguards Review Tooling</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5342935008</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Technical Program Manager, Safeguards (Infrastructure &amp; Evals)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5108695008</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Threat Intel Manager, Model Exploitation &amp; Fraud</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5305476008</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Credit Risk Strategy and Analytics</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Risk Strategy</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8044686</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Credit Risk Strategy and Analytics </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">United States </t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Risk Strategy</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8052468</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Credit Risk Strategy Manager</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Risk Strategy</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7863824</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Fraud Operations Associate SDC</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Mexico City</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7651078</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Fraud Operations Manager</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7608396</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Fraud Operations Manager (Mandarin-speaking)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7994541</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Fraud Operations Team Lead</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Mexico City</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7685460</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Fraud Operations Team Lead</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8063857</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Fraud Patterns Analyst</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>US-Remote</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7913410</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Fraud Strategist</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">United States </t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8039803</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fraud Strategy Manager </t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Remote </t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8039729</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Head of User Risk Strategy</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Risk Strategy</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7730667</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineering Manager - Fraud Detection</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8069506</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Payments Fraud Investigator</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Dublin</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7554002</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Payments Fraud Investigator</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>US-Remote</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7913406</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Specialist Solutions Architect, Radar (Fraud/Risk)</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NY or SF</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7365914</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>User Risk Strategist, Ecosystem Risk Strategy</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>US-Chicago; US-Atlanta; US-Remote</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Risk Strategy</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7977981</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Finance Business Partner, Trust &amp; Safety (6319)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, United States</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>https://careers.roblox.com/jobs/7977161?gh_jid=7977161</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Senior Product Policy Manager, Regional Policy (Europe)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Amsterdam, North Holland, Netherlands</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Product Policy</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://careers.roblox.com/jobs/7962542?gh_jid=7962542</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Senior Product Policy Manager, Regional Policy (LATAM)</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>São Paulo, Brazil</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Product Policy</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://careers.roblox.com/jobs/7928938?gh_jid=7928938</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Senior Product Policy Manager, Regional Policy (SEA/ SA)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Gurugram, Haryana, India; India</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Product Policy</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>https://careers.roblox.com/jobs/8012671?gh_jid=8012671</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Senior Product Policy Manager, Regional Policy (SEA/SA)</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Product Policy</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://careers.roblox.com/jobs/7981917?gh_jid=7981917</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Roblox</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Fraud</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, United States</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://careers.roblox.com/jobs/8008607?gh_jid=8008607</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Sr. Data Scientist, Trust and Safety</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US; Remote, CA, US</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7793344</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Sr. Machine Learning Engineer, Responsible AI– Applied Research Science</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US; Remote, CA, US</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Responsible AI</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7494938</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Block/Cash App</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Staff Applied Machine Learning Engineer - Fraud &amp; Abuse</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Bay Area, CA, United States of America</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>http://block.xyz/careers/jobs/4969342008?gh_jid=4969342008</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Robinhood</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Software Developer, Ops Platform and Fraud Investigations</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Toronto, Canada</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/7737164?t=gh_src=&amp;gh_jid=7737164</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Product Manager, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8530184002?gh_jid=8530184002</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Ramp</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Software Engineer, Fraud &amp; Identity</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>New York, NY (HQ)</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/ramp/8fa367de-71ba-409e-befd-175a163acb1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Fraud &amp; Identity Specialist (Contract)</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>United States - Remote</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://instacart.careers/job/?gh_jid=4995818</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety Specialist, Law Enforcement Response</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>United States - Remote</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://instacart.careers/job/?gh_jid=8001105</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2476,58 +2530,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3372,58 +3426,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +414,3004 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F93"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Biological Safety Research Scientist</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safety Research</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5066977008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Data Scientist, Safeguards</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York City, NY; San Francisco, CA; Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5209196008</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Safeguards Interventions</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5322723008</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Safeguards Review Tooling</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5013366008</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ML/Research Engineer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4949336008</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Product Manager, Safeguards (Child Safety)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5164820008</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Product Manager, Safeguards Rare Harms</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5139628008</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Product Manager, Safeguards (Verticals)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5097490008</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Red Team Engineer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel Required) | San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5320469008</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Research Engineer (Senior Staff+), Safeguards Labs</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5191785008</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Access Controls &amp; Identity</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319626008</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Account Takeover &amp; Credential Abuse</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319624008</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Age-Appropriate Design</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311234008</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Ban Evasion &amp; Recidivism</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319592008</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Bio Harms</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319696008</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Chem &amp; Explosives Harms</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319700008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Child Safety</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311237008</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safeguards Enforcement Analyst, Cyber Harm </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311159008</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Fraud &amp; Scams</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Safeguards, Fraud</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319554008</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Safeguards Enforcement Analyst, Integrity &amp; Authenticity </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5311149008</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Radiological &amp; Nuclear Harms</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5319702008</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Safety Evaluations</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Washington, DC; San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Safeguards, Safety Evaluations</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5137183008</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Violence &amp; Extremism</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5343907008</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Safeguards Policy Analyst, Fraud &amp; Scams</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Safeguards, Fraud</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5174857008</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Financial Fraud</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5325909008</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4951844008</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Evals </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5251671008</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Infrastructure </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5074908008</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Safeguards ML Infrastructure</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/4778843008</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Staff+ Software Engineer, Safeguards Review Tooling</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5342935008</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Technical Program Manager, Safeguards (Infrastructure &amp; Evals)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5108695008</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Threat Intel Manager, Model Exploitation &amp; Fraud</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5305476008</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Technical Lead, Safety Research</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Safety Research</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/273b4c99-273e-4a70-aff9-19c0d959dcef</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Operations Analyst, Ads</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/c9e9e3a5-fb93-4162-b876-6266016819c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Product Policy, Biosecurity Policy Manager</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/8b1f58e8-2922-4d55-bce6-04d7b4c5ec21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Technical Lead Manager, Data Engineering, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/e1daa4e0-c42a-45a7-b9ee-559b35bfe08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Operations Analyst, Ads</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/26e8c199-7dcb-4144-b263-f35220421a6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Credit Risk Strategy and Analytics</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8044686</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credit Risk Strategy and Analytics </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8052468</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Credit Risk Strategy Manager</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7863824</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Fraud Operations Associate SDC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8066310</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fraud Operations Associate SDC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7651078</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Fraud Operations Manager</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7608396</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Fraud Operations Manager (Mandarin-speaking)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7994541</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fraud Operations Team Lead</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7685460</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fraud Operations Team Lead</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8063857</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fraud Patterns Analyst</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>US-Remote</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7913410</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fraud Strategist</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8039803</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fraud Strategy Manager </t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remote </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8039729</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Head of User Risk Strategy</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7730667</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineering Manager - Fraud Detection</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8069506</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Payments Fraud Investigator</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>US-Remote</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7913406</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Payments Fraud Investigator</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Dublin</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7554002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect, Radar (Fraud/Risk)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NY or SF</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7365914</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>User Risk Strategist, Ecosystem Risk Strategy</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>US-Chicago; US-Atlanta; US-Remote</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=7977981</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Finance Business Partner, Trust &amp; Safety (6319)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7977161?gh_jid=7977161</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (Europe)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Amsterdam, North Holland, Netherlands</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7962542?gh_jid=7962542</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (LATAM)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>São Paulo, Brazil</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7928938?gh_jid=7928938</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (SEA/ SA)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Gurugram, Haryana, India; India</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/8012671?gh_jid=8012671</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Senior Product Policy Manager, Regional Policy (SEA/SA)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/7981917?gh_jid=7981917</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Roblox</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Fraud</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, United States</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://careers.roblox.com/jobs/8008607?gh_jid=8008607</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Trust and Safety</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Remote, CA, US</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7793344</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning Engineer, Responsible AI– Applied Research Science</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US; Remote, CA, US</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Responsible AI</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7494938</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Block/Cash App</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Staff Applied Machine Learning Engineer - Fraud &amp; Abuse</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Bay Area, CA, United States of America</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>http://block.xyz/careers/jobs/4969342008?gh_jid=4969342008</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Software Developer, Ops Platform and Fraud Investigations</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Toronto, Canada</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7737164?t=gh_src=&amp;gh_jid=7737164</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Chime</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Product Manager, Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Chicago, IL, USA; San Francisco, CA, USA</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/chime/jobs/8530184002?gh_jid=8530184002</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Senior Fraud and Abuse Operations Analyst</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>New York City Office</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/ba4a5f3e-aea0-422e-9f50-2b23f90281aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Fraud and Abuse Operations Analyst</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/02569523-bd54-4f1f-b88e-38beef2f824d</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Fraud Solutions Consultant</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>New York City Office</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/6dbf0f7f-ef35-4037-9418-6b2460f41345</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Senior Fraud Research Analyst</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/1bcfe93d-97bd-4618-b81e-dc308ef69d30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer - (Payment Risk/Fraud) - Embedded Insights</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/50d40e3b-ed34-470d-b094-71e1555c6f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - (Payment Risk/Fraud) Embedded Insights</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/9d60d913-8a99-4d52-9960-dbeb7e65cfa3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Product Manager, Fraud Data</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/bda0f40d-5ac5-4ea4-aaab-3e5e013c0a26</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Account Executive - Fraud</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/3a0611c3-7b8e-4962-bb48-dcd7ba04f352</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Software Engineer, Fraud &amp; Identity</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>New York, NY (HQ)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/ramp/8fa367de-71ba-409e-befd-175a163acb1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fraud &amp; Identity Specialist (Contract)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=4995818</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety Specialist, Law Enforcement Response</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8001105</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst -  Trust, Safety, and Fraud Analytics</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/rover/a79df802-9fbc-42af-a698-44ac68ab538f</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Platform Integrity Lead</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>New York, NY</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Platform Integrity</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/spotify/76a2bac9-855a-403c-8832-b378a5507a0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Manager, Fraud Intelligence</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/7793861?gh_jid=7793861</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Senior Manager, Advanced Analytics, Fraud &amp; Safety Operations</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/7788160?gh_jid=7788160</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Senior Platform Manager, Trust and Safety</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">United States </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/8029984?gh_jid=8029984</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Supervisor, Fraud Investigations</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Gurugram, India</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://careers.airbnb.com/positions/8007130?gh_jid=8007130</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fraud Strategist - Ecosystem</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UT - Cottonwood Heights; FL - Jacksonville; CA - San Francisco; NY - New York; WA - Seattle; NC -Charlotte; TX - Frisco; DE - Greenville</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://sofi.com/careers/job/7789709003?gh_jid=7789709003</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Fraud Strategist - Login and Auth</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UT - Cottonwood Heights; FL - Jacksonville; CA - San Francisco; NY - New York; WA - Seattle; NC -Charlotte; TX - Frisco; DE - Greenville</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://sofi.com/careers/job/7789705003?gh_jid=7789705003</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Staff Fraud Analyst</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NY - New York</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://sofi.com/careers/job/7698656003?gh_jid=7698656003</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager: Trust &amp; Safety, Community</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Seattle, WA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8536449002</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager: Trust &amp; Safety, Community</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Irvine, CA</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8536452002</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager: Trust &amp; Safety, Community</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8529558002</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Product Marketing Manager: Trust &amp; Safety, Community</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>San Francisco, CA</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8536451002</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Senior Trust and Safety Operations Analyst</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sydney, Australia</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8596758002</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Twitch</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Trust and Safety Analyst</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/twitch/jobs/8590327002</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3404,58 +3458,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fraud Investigations Analyst </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Denver, CO; Westlake, TX</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/robinhood/jobs/7729808?t=gh_src=&amp;gh_jid=7729808</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,32 +460,128 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fraud Investigations Analyst </t>
+          <t>[C] Data Engineer, Safeguards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Denver, CO; Westlake, TX</t>
+          <t>San Francisco, CA | New York City, NY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5247446008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Machine Learning Infrastructure Engineer, Safeguards Research</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5364804008</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Staff Product Manager, Ads Trust and Safety</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Remote - United States</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8070669</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Staff Product Manager - Fraud</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>Fraud</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/robinhood/jobs/7729808?t=gh_src=&amp;gh_jid=7729808</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/779a5b90-8630-472a-b819-3710486ef7e9</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,134 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>[C] Data Engineer, Safeguards</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5247446008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Machine Learning Infrastructure Engineer, Safeguards Research</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5364804008</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Staff Product Manager, Ads Trust and Safety</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8070669</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Plaid</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Staff Product Manager - Fraud</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>San Francisco HQ</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/plaid/779a5b90-8630-472a-b819-3710486ef7e9</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Data Engineer, Safeguards</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5240422008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Data Engineer, Safeguards</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5240422008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3276,58 +3330,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Product Policy - Youth Policy Manager</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/c20ea3d3-76a6-438d-9bb5-c9be97917975</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -419,10 +419,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,32 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Product Policy - Youth Policy Manager</t>
+          <t>Risk Strategist, Platform Risk Strategy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t xml:space="preserve">Chicago, US-Remote, Toronto </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Product Policy</t>
+          <t>Risk Strategy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/c20ea3d3-76a6-438d-9bb5-c9be97917975</t>
+          <t>https://stripe.com/jobs/search?gh_jid=7811937</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,22 +470,54 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk Strategist, Platform Risk Strategy</t>
+          <t>Fraud Operations Associate (Mandarin Speaking)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chicago, US-Remote, Toronto </t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Risk Strategy</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=7811937</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8076652</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fraud Analyst (Revenue Protection) - 12-Month Fixed-Term</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/spotify/5992c673-e493-48b1-bb63-9b82a4c31876</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,70 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Fraud Operations Associate (Mandarin Speaking)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8076652</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Spotify</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fraud Analyst (Revenue Protection) - 12-Month Fixed-Term</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/spotify/5992c673-e493-48b1-bb63-9b82a4c31876</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3340,58 +3394,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, User Well-being</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5374778008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -418,11 +418,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="59" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,32 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>SoFi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Safeguards Enforcement Analyst, User Well-being</t>
+          <t>Fraud Model Developer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Remote-Friendly, United States; San Francisco, CA | New York City, NY | Washington, DC</t>
+          <t xml:space="preserve">Frisco, TX </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Safeguards</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5374778008</t>
+          <t>https://sofi.com/careers/job/7826869003?gh_jid=7826869003</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -419,10 +419,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="59" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,32 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Roblox</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fraud Model Developer</t>
+          <t xml:space="preserve">Senior Product Policy Manager, Monetization   </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frisco, TX </t>
+          <t>San Mateo, CA, United States</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Product Policy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://sofi.com/careers/job/7826869003?gh_jid=7826869003</t>
+          <t>https://careers.roblox.com/jobs/8106959?gh_jid=8106959</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -419,10 +419,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="56" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,32 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Roblox</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Senior Product Policy Manager, Monetization   </t>
+          <t>Data Scientist, Fraud</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Mateo, CA, United States</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Product Policy</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://careers.roblox.com/jobs/8106959?gh_jid=8106959</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8113100</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="59" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,12 +470,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Data Scientist, Fraud</t>
+          <t>Fraud Operations Associate SDC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,7 +485,39 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8113100</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8063717</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pinterest</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Trust &amp; Safety and Content Quality</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Toronto, ON, CA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trust &amp; Safety</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8092378</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="59" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,70 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Fraud Operations Associate SDC</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8063717</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist, Trust &amp; Safety and Content Quality</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Toronto, ON, CA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8092378</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3244,58 +3298,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Staff+ Site Reliability Engineer, Safeguards ML Infra</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Seattle, WA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5230394008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,22 +460,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Staff+ Site Reliability Engineer, Safeguards ML Infra</t>
+          <t>Technical Program Manager, AI Safety &amp; Safeguards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Seattle, WA | New York City, NY</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,7 +485,135 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5230394008</t>
+          <t>https://jobs.ashbyhq.com/openai/60b966d1-9c7f-4f61-b05e-7bda3e0b0a69</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fraud Operartions Associate</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Seattle, Washington, United States</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8698277002?gh_jid=8698277002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fraud Operartions Associate</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>San Francisco, California, United States</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8698276002?gh_jid=8698276002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fraud Operartions Associate</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New York, New York, United States</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8698248002?gh_jid=8698248002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Brex</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fraud Operartions Associate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Salt Lake City, Utah, United States</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.brex.com/careers/8698160002?gh_jid=8698160002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,160 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technical Program Manager, AI Safety &amp; Safeguards</t>
+          <t>Fraud &amp; Risk Analyst</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Toronto, Canada</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Safeguards</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/openai/60b966d1-9c7f-4f61-b05e-7bda3e0b0a69</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fraud Operartions Associate</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Seattle, Washington, United States</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8698277002?gh_jid=8698277002</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fraud Operartions Associate</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>San Francisco, California, United States</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8698276002?gh_jid=8698276002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Fraud Operartions Associate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>New York, New York, United States</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8698248002?gh_jid=8698248002</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fraud Operartions Associate</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Salt Lake City, Utah, United States</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8698160002?gh_jid=8698160002</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8697534002?gh_jid=8697534002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Lyft</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Fraud &amp; Risk Analyst</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Toronto, Canada</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8697534002?gh_jid=8697534002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,70 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Data </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5379140008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Product Policy Research and Advisory Partnerships</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/openai/978a22a5-0f0f-4da7-811e-a4b2b2fbe659</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,70 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Staff+ Software Engineer, Safeguards Data </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5379140008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Product Policy Research and Advisory Partnerships</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Product Policy</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/openai/978a22a5-0f0f-4da7-811e-a4b2b2fbe659</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Weekly Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Daily New" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily New" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly Snapshot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,6 +414,60 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date Found</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Matched Keywords</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3436,58 +3490,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Date Found</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Matched Keywords</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,102 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fraud Intelligence Lead</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>New York City Office</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/5ea24e42-7bd8-48e9-9f60-d09db6288d81</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Fraud &amp; Identity Platform</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>United States - Remote</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8137846</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Engineering Manager, Fraud &amp; Identity Platform</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Canada - Remote (ON, AB, BC, or NS Only)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://instacart.careers/job/?gh_jid=8137847</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,96 +460,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Plaid</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fraud Intelligence Lead</t>
+          <t>Technical Program Manager, AI Safety &amp; Safeguards</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>New York City Office</t>
+          <t>San Francisco</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Safeguards</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/plaid/5ea24e42-7bd8-48e9-9f60-d09db6288d81</t>
+          <t>https://jobs.ashbyhq.com/openai/3a05c5d7-fdd9-4e0e-823a-2ae08b59958b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Chime</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Engineering Manager, Fraud &amp; Identity Platform</t>
+          <t>Sr. Product Marketing Manager, Trust &amp; Safety</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United States - Remote</t>
+          <t>San Francisco, CA, USA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Trust &amp; Safety</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://instacart.careers/job/?gh_jid=8137846</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Instacart</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Engineering Manager, Fraud &amp; Identity Platform</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Canada - Remote (ON, AB, BC, or NS Only)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://instacart.careers/job/?gh_jid=8137847</t>
+          <t>https://boards.greenhouse.io/chime/jobs/8694719002?gh_jid=8694719002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,70 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Technical Program Manager, AI Safety &amp; Safeguards</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>San Francisco</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/openai/3a05c5d7-fdd9-4e0e-823a-2ae08b59958b</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sr. Product Marketing Manager, Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trust &amp; Safety</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8694719002?gh_jid=8694719002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Safeguards Policy Analyst, Cyber Harms</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco, CA | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5397711008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,12 +470,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Safeguards Policy Analyst, Cyber Harms</t>
+          <t>Senior Safeguards Policy Lead, Cyber Harms</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco, CA | Washington, DC</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,7 +485,135 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5397711008</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5397708008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fraud Strategist</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LOCATION</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8112448</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Social Media Specialist (Trust and Safety)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/rover/fda6e912-02c1-4bd8-9fde-6df2905be5b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fraud Strategist, Business &amp; Commercial Banking</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TX - Frisco</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://sofi.com/careers/job/7920087003?gh_jid=7920087003</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Principal Fraud Strategist, Authentication and Device Trust</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TX - Frisco</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://sofi.com/careers/job/7920083003?gh_jid=7920083003</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,166 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Senior Safeguards Policy Lead, Cyber Harms</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Washington, DC</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5397708008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fraud Strategist</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LOCATION</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8112448</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Rover</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Social Media Specialist (Trust and Safety)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Remote</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/rover/fda6e912-02c1-4bd8-9fde-6df2905be5b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Fraud Strategist, Business &amp; Commercial Banking</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TX - Frisco</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://sofi.com/careers/job/7920087003?gh_jid=7920087003</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SoFi</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Principal Fraud Strategist, Authentication and Device Trust</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TX - Frisco</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://sofi.com/careers/job/7920083003?gh_jid=7920083003</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Product Policy Manager, Product Risk</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Seattle, WA | New York City, NY</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Product Policy</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5400010008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,32 +460,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Rover</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Product Policy Manager, Product Risk</t>
+          <t>Trust and Safety Agent - French Speaking</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Seattle, WA | New York City, NY</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Product Policy</t>
+          <t>Trust and Safety</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5400010008</t>
+          <t>https://jobs.lever.co/rover/7cd71faa-5b4b-4476-ace6-0a19623569cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trust and Safety Agent - German Speaking</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/rover/1c334d74-861c-4872-8906-499e1d4202ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Risk Strategy Execution Analyst</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UT - Cottonwood Heights</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Risk Strategy</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://sofi.com/careers/job/7920073003?gh_jid=7920073003</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,54 +460,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rover</t>
+          <t>Pinterest</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trust and Safety Agent - French Speaking</t>
+          <t>Machine Learning Engineer II, Responsible AI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>San Francisco, CA, US; Remote, US</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trust and Safety</t>
+          <t>Responsible AI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/rover/7cd71faa-5b4b-4476-ace6-0a19623569cf</t>
+          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rover</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Trust and Safety Agent - German Speaking</t>
+          <t>Trust and Safety Policy, Ads Policy,  Lead</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Remote - United States</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,39 +517,135 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/rover/1c334d74-861c-4872-8906-499e1d4202ce</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8159077</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SoFi</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk Strategy Execution Analyst</t>
+          <t>Fraud Operations Associate</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UT - Cottonwood Heights</t>
+          <t>Vancouver, British Columbia, Canada</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Risk Strategy</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://sofi.com/careers/job/7920073003?gh_jid=7920073003</t>
+          <t>https://www.brex.com/careers/8750674002?gh_jid=8750674002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Patreon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fraud Specialist</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/patreon/37b9ae12-b503-42b7-b16e-ee6281c6a0c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Trust and Safety Agent - French Speaking (Tue-Sat)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/rover/a9df3669-d156-4d19-ab06-1e3e2dab2f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Trust and Safety Agent - German Speaking (Tue-Sat)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/rover/2acc93fa-a8e5-4c9a-811e-44542637c884</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="53" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,192 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pinterest</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Responsible AI</t>
+          <t>Product Manager, Multi-Cloud Trust &amp; Safety</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US; Remote, US</t>
+          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Responsible AI</t>
+          <t>Trust &amp; Safety</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=8162046</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Trust and Safety Policy, Ads Policy,  Lead</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Remote - United States</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8159077</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Fraud Operations Associate</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Vancouver, British Columbia, Canada</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8750674002?gh_jid=8750674002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Patreon</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Fraud Specialist</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Porto</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Fraud</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/patreon/37b9ae12-b503-42b7-b16e-ee6281c6a0c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Rover</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Trust and Safety Agent - French Speaking (Tue-Sat)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/rover/a9df3669-d156-4d19-ab06-1e3e2dab2f98</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Rover</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Trust and Safety Agent - German Speaking (Tue-Sat)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/rover/2acc93fa-a8e5-4c9a-811e-44542637c884</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5409934008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -419,8 +419,8 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="53" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,22 +470,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Product Manager, Multi-Cloud Trust &amp; Safety</t>
+          <t>Safeguards Enforcement Lead, Cyber Harms</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
+          <t>Remote-Friendly (Travel-Required) |  Washington, DC; San Francisco, CA | New York City, NY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trust &amp; Safety</t>
+          <t>Safeguards</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5409934008</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5403775008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Lead, Cyber Harms</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Remote-Friendly (Travel-Required) |  Washington, DC; San Francisco, CA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5403775008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,102 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering Manager, Safeguards </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5410610008</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Analyst, Conventional Weapons</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York City, NY; Remote-Friendly (Travel-Required) | San Francisco, CA | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5410006008</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Safeguards Enforcement Lead, User Well-Being</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New York City, NY; Remote-Friendly (Travel-Required) | San Francisco, CA | Washington, DC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Safeguards</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5410004008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="54" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,102 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Engineering Manager, Safeguards </t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5410610008</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Analyst, Conventional Weapons</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>New York City, NY; Remote-Friendly (Travel-Required) | San Francisco, CA | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5410006008</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Safeguards Enforcement Lead, User Well-Being</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>New York City, NY; Remote-Friendly (Travel-Required) | San Francisco, CA | Washington, DC</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5410004008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Discord</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Payments &amp; Fraud Analyst</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/discord/jobs/8771059002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -418,11 +418,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,32 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Discord</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Payments &amp; Fraud Analyst</t>
+          <t>Staff+ Site Reliability Engineer, Safeguards ML Infra</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area</t>
+          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Seattle, WA | New York City, NY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Safeguards</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/discord/jobs/8771059002</t>
+          <t>https://job-boards.greenhouse.io/anthropic/jobs/5416709008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,38 +454,6 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-05</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Staff+ Site Reliability Engineer, Safeguards ML Infra</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Remote-Friendly (Travel-Required) | San Francisco, CA | Seattle, WA | New York City, NY</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Safeguards</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5416709008</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,6 +454,38 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fraud Operations Manager</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>US-Remote</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://stripe.com/jobs/search?gh_jid=8175832</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -419,10 +419,10 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="47" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Lyft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fraud Operations Manager</t>
+          <t>Fraud and Risk Specialist</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>US-Remote</t>
+          <t>Nashville, TN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8175832</t>
+          <t>https://app.careerpuck.com/job-board/lyft/job/8786114002?gh_jid=8786114002</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,32 +460,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fraud and Risk Specialist</t>
+          <t>Trust and Safety Policy, Ads Policy,  Lead (Europe)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nashville, TN</t>
+          <t>Remote - The Netherlands</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fraud</t>
+          <t>Trust and Safety</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://app.careerpuck.com/job-board/lyft/job/8786114002?gh_jid=8786114002</t>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8190630</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trust and Safety Policy, Ads Policy,  Lead (Europe)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Remote - United Kingdom</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8190627</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Trust and Safety Policy, Ads Policy,  Lead (Europe)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Remote - Ireland</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Trust and Safety</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/reddit/jobs/8188275</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,15 +414,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,96 +460,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Plaid</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Trust and Safety Policy, Ads Policy,  Lead (Europe)</t>
+          <t>Account Executive - Fraud</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Remote - The Netherlands</t>
+          <t>Raleigh Office</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Trust and Safety</t>
+          <t>Fraud</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8190630</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Trust and Safety Policy, Ads Policy,  Lead (Europe)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Remote - United Kingdom</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8190627</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Trust and Safety Policy, Ads Policy,  Lead (Europe)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Remote - Ireland</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Trust and Safety</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/reddit/jobs/8188275</t>
+          <t>https://jobs.ashbyhq.com/plaid/d2f89c8e-551d-402b-9e81-c42577292d63</t>
         </is>
       </c>
     </row>

--- a/data/jobs.xlsx
+++ b/data/jobs.xlsx
@@ -414,13 +414,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
@@ -460,7 +460,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -470,12 +470,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Account Executive - Fraud</t>
+          <t>Fraud Data Partnerships</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Raleigh Office</t>
+          <t>San Francisco HQ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -485,7 +485,167 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/plaid/d2f89c8e-551d-402b-9e81-c42577292d63</t>
+          <t>https://jobs.ashbyhq.com/plaid/4003dc3c-5714-4449-bf65-ac0c7d5385e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Data Scientist - Fraud</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>New York City Office</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/361c4725-ab72-4895-a3aa-9b642f4927a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Data Science Manager - Fraud</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>New York City Office</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/55eacfa6-71e0-42ac-8788-04dc1e5fd694</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Infra/Ops - Fraud</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>New York City Office</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/e9a9aeab-be90-43f3-b898-63a846cb5777</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer (Research Scientist) - Fraud</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>New York City Office</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/5e56c0a6-3caa-4255-8c63-95c29cbc2a32</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer - Fraud</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>San Francisco HQ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fraud</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://jobs.ashbyhq.com/plaid/85cd5d07-9920-45fa-931a-daf8c3558e5b</t>
         </is>
       </c>
     </row>
